--- a/IPC_SubClase.xlsx
+++ b/IPC_SubClase.xlsx
@@ -681,10 +681,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>0.01182831586070351</v>
+        <v>0.0118283158607035</v>
       </c>
       <c r="C3" s="2">
-        <v>135.9165028204382</v>
+        <v>135.9165028204383</v>
       </c>
       <c r="D3" s="2">
         <v>0.0118283158607035</v>
@@ -726,7 +726,7 @@
         <v>0.009279354150038282</v>
       </c>
       <c r="C6" s="2">
-        <v>121.336810766649</v>
+        <v>121.3368107666489</v>
       </c>
       <c r="D6" s="2">
         <v>0.00927935415003828</v>
@@ -751,13 +751,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>0.06938042960518691</v>
+        <v>0.06938042960518689</v>
       </c>
       <c r="C8" s="2">
-        <v>110.6083845460439</v>
+        <v>110.608384546044</v>
       </c>
       <c r="D8" s="2">
-        <v>0.06938042960518689</v>
+        <v>0.06938042960518688</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -782,7 +782,7 @@
         <v>0.0328873179022003</v>
       </c>
       <c r="C10" s="2">
-        <v>109.1725792411427</v>
+        <v>109.1725792411426</v>
       </c>
       <c r="D10" s="2">
         <v>0.03288731790220029</v>
@@ -807,13 +807,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>0.0008425152421623416</v>
+        <v>0.0008425152421623413</v>
       </c>
       <c r="C12" s="2">
         <v>147.0733031615884</v>
       </c>
       <c r="D12" s="2">
-        <v>0.0008425152421623413</v>
+        <v>0.0008425152421623411</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -905,13 +905,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2">
-        <v>0.004871767549653516</v>
+        <v>0.004871767549653517</v>
       </c>
       <c r="C19" s="2">
         <v>121.444736749867</v>
       </c>
       <c r="D19" s="2">
-        <v>0.004871767549653515</v>
+        <v>0.004871767549653516</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -925,7 +925,7 @@
         <v>126.525520444729</v>
       </c>
       <c r="D20" s="2">
-        <v>0.002628894483991282</v>
+        <v>0.002628894483991281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -947,13 +947,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="2">
-        <v>0.003717969600974466</v>
+        <v>0.003717969600974467</v>
       </c>
       <c r="C22" s="2">
         <v>102.0214339331879</v>
       </c>
       <c r="D22" s="2">
-        <v>0.003717969600974465</v>
+        <v>0.003717969600974466</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -992,10 +992,10 @@
         <v>0.02820800969598953</v>
       </c>
       <c r="C25" s="2">
-        <v>107.0959146621802</v>
+        <v>107.0959146621803</v>
       </c>
       <c r="D25" s="2">
-        <v>0.02820800969598953</v>
+        <v>0.02820800969598952</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1017,7 +1017,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="2">
-        <v>0.001829311596817195</v>
+        <v>0.001829311596817196</v>
       </c>
       <c r="C27" s="2">
         <v>125.6420830245765</v>
@@ -1065,7 +1065,7 @@
         <v>139.3014956247881</v>
       </c>
       <c r="D30" s="2">
-        <v>0.002364321672286093</v>
+        <v>0.002364321672286094</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1076,10 +1076,10 @@
         <v>0.00141595456186346</v>
       </c>
       <c r="C31" s="2">
-        <v>126.7690899726294</v>
+        <v>126.7690899726295</v>
       </c>
       <c r="D31" s="2">
-        <v>0.001415954561863459</v>
+        <v>0.00141595456186346</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1090,7 +1090,7 @@
         <v>0.01658644706594438</v>
       </c>
       <c r="C32" s="2">
-        <v>122.1846224776652</v>
+        <v>122.1846224776651</v>
       </c>
       <c r="D32" s="2">
         <v>0.01658644706594438</v>
@@ -1101,13 +1101,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="2">
-        <v>0.00846561094788917</v>
+        <v>0.008465610947889168</v>
       </c>
       <c r="C33" s="2">
         <v>116.4399953525779</v>
       </c>
       <c r="D33" s="2">
-        <v>0.008465610947889168</v>
+        <v>0.008465610947889167</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1146,7 +1146,7 @@
         <v>0.01036117432565099</v>
       </c>
       <c r="C36" s="2">
-        <v>120.8468299670843</v>
+        <v>120.8468299670844</v>
       </c>
       <c r="D36" s="2">
         <v>0.01036117432565099</v>
@@ -1219,7 +1219,7 @@
         <v>120.7050459353101</v>
       </c>
       <c r="D41" s="2">
-        <v>0.003658040834499998</v>
+        <v>0.003658040834499999</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1227,13 +1227,13 @@
         <v>44</v>
       </c>
       <c r="B42" s="2">
-        <v>0.008997473089557801</v>
+        <v>0.008997473089557805</v>
       </c>
       <c r="C42" s="2">
         <v>102.2454321049577</v>
       </c>
       <c r="D42" s="2">
-        <v>0.008997473089557799</v>
+        <v>0.008997473089557803</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1255,13 +1255,13 @@
         <v>46</v>
       </c>
       <c r="B44" s="2">
-        <v>0.007203136928336721</v>
+        <v>0.007203136928336722</v>
       </c>
       <c r="C44" s="2">
         <v>115.3664788537881</v>
       </c>
       <c r="D44" s="2">
-        <v>0.007203136928336719</v>
+        <v>0.007203136928336721</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1272,7 +1272,7 @@
         <v>0.01381749199465612</v>
       </c>
       <c r="C45" s="2">
-        <v>111.8584076785985</v>
+        <v>111.8584076785986</v>
       </c>
       <c r="D45" s="2">
         <v>0.01381749199465612</v>
@@ -1297,13 +1297,13 @@
         <v>49</v>
       </c>
       <c r="B47" s="2">
-        <v>0.002771663492127025</v>
+        <v>0.002771663492127026</v>
       </c>
       <c r="C47" s="2">
         <v>110.2608888292721</v>
       </c>
       <c r="D47" s="2">
-        <v>0.002771663492127025</v>
+        <v>0.002771663492127026</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1311,13 +1311,13 @@
         <v>50</v>
       </c>
       <c r="B48" s="2">
-        <v>0.004287135021955557</v>
+        <v>0.004287135021955558</v>
       </c>
       <c r="C48" s="2">
         <v>140.1677028555776</v>
       </c>
       <c r="D48" s="2">
-        <v>0.004287135021955556</v>
+        <v>0.004287135021955557</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1339,13 +1339,13 @@
         <v>52</v>
       </c>
       <c r="B50" s="2">
-        <v>0.0005641748576908801</v>
+        <v>0.00056417485769088</v>
       </c>
       <c r="C50" s="2">
         <v>122.5725893240119</v>
       </c>
       <c r="D50" s="2">
-        <v>0.00056417485769088</v>
+        <v>0.0005641748576908799</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1353,7 +1353,7 @@
         <v>53</v>
       </c>
       <c r="B51" s="2">
-        <v>0.003340150088683029</v>
+        <v>0.003340150088683028</v>
       </c>
       <c r="C51" s="2">
         <v>124.9914840788052</v>
@@ -1367,10 +1367,10 @@
         <v>54</v>
       </c>
       <c r="B52" s="2">
-        <v>0.01581383143594381</v>
+        <v>0.01581383143594382</v>
       </c>
       <c r="C52" s="2">
-        <v>104.514083312447</v>
+        <v>104.5140833124469</v>
       </c>
       <c r="D52" s="2">
         <v>0.01581383143594381</v>
@@ -1384,7 +1384,7 @@
         <v>0.02640314655717807</v>
       </c>
       <c r="C53" s="2">
-        <v>103.5078100383202</v>
+        <v>103.5078100383201</v>
       </c>
       <c r="D53" s="2">
         <v>0.02640314655717807</v>
@@ -1401,7 +1401,7 @@
         <v>104.6241275631374</v>
       </c>
       <c r="D54" s="2">
-        <v>0.004720451181454748</v>
+        <v>0.004720451181454747</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1465,7 +1465,7 @@
         <v>61</v>
       </c>
       <c r="B59" s="2">
-        <v>0.03742400034954897</v>
+        <v>0.03742400034954898</v>
       </c>
       <c r="C59" s="2">
         <v>110.7120497459299</v>
@@ -1479,7 +1479,7 @@
         <v>62</v>
       </c>
       <c r="B60" s="2">
-        <v>0.001016325943373207</v>
+        <v>0.001016325943373208</v>
       </c>
       <c r="C60" s="2">
         <v>130.7478489306803</v>
@@ -1499,7 +1499,7 @@
         <v>110.8521113458137</v>
       </c>
       <c r="D61" s="2">
-        <v>0.03095859502448804</v>
+        <v>0.03095859502448803</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1510,7 +1510,7 @@
         <v>0.01026379595995948</v>
       </c>
       <c r="C62" s="2">
-        <v>116.3331782267851</v>
+        <v>116.3331782267852</v>
       </c>
       <c r="D62" s="2">
         <v>0.01026379595995948</v>
@@ -1524,7 +1524,7 @@
         <v>0.007749148682337151</v>
       </c>
       <c r="C63" s="2">
-        <v>111.2763649678526</v>
+        <v>111.2763649678527</v>
       </c>
       <c r="D63" s="2">
         <v>0.007749148682337149</v>
@@ -1535,7 +1535,7 @@
         <v>66</v>
       </c>
       <c r="B64" s="2">
-        <v>0.002092316115213713</v>
+        <v>0.002092316115213712</v>
       </c>
       <c r="C64" s="2">
         <v>104.1162443810259</v>
@@ -1549,13 +1549,13 @@
         <v>67</v>
       </c>
       <c r="B65" s="2">
-        <v>0.007477431255628968</v>
+        <v>0.007477431255628969</v>
       </c>
       <c r="C65" s="2">
         <v>111.9958208906215</v>
       </c>
       <c r="D65" s="2">
-        <v>0.007477431255628966</v>
+        <v>0.007477431255628967</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1591,13 +1591,13 @@
         <v>70</v>
       </c>
       <c r="B68" s="2">
-        <v>0.003897798195780221</v>
+        <v>0.00389779819578022</v>
       </c>
       <c r="C68" s="2">
         <v>100.8199980162666</v>
       </c>
       <c r="D68" s="2">
-        <v>0.00389779819578022</v>
+        <v>0.003897798195780219</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1605,7 +1605,7 @@
         <v>71</v>
       </c>
       <c r="B69" s="2">
-        <v>0.002520586117202039</v>
+        <v>0.002520586117202038</v>
       </c>
       <c r="C69" s="2">
         <v>109.8211612559688</v>
@@ -1650,7 +1650,7 @@
         <v>0.01232422405380983</v>
       </c>
       <c r="C72" s="2">
-        <v>121.3181369215623</v>
+        <v>121.3181369215622</v>
       </c>
       <c r="D72" s="2">
         <v>0.01232422405380983</v>
@@ -1675,10 +1675,10 @@
         <v>76</v>
       </c>
       <c r="B74" s="2">
-        <v>0.002520198233826913</v>
+        <v>0.002520198233826914</v>
       </c>
       <c r="C74" s="2">
-        <v>101.9258256639823</v>
+        <v>101.9258256639824</v>
       </c>
       <c r="D74" s="2">
         <v>0.002520198233826913</v>
@@ -1689,13 +1689,13 @@
         <v>77</v>
       </c>
       <c r="B75" s="2">
-        <v>0.00273576606798322</v>
+        <v>0.002735766067983221</v>
       </c>
       <c r="C75" s="2">
         <v>142.9717145523893</v>
       </c>
       <c r="D75" s="2">
-        <v>0.002735766067983219</v>
+        <v>0.00273576606798322</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1706,7 +1706,7 @@
         <v>0.02484337017518047</v>
       </c>
       <c r="C76" s="2">
-        <v>120.9561136190862</v>
+        <v>120.9561136190863</v>
       </c>
       <c r="D76" s="2">
         <v>0.02484337017518046</v>
@@ -1731,10 +1731,10 @@
         <v>80</v>
       </c>
       <c r="B78" s="2">
-        <v>0.1255960997460793</v>
+        <v>0.1255960997460794</v>
       </c>
       <c r="C78" s="2">
-        <v>116.2152990360026</v>
+        <v>116.2152990360027</v>
       </c>
       <c r="D78" s="2">
         <v>0.1255960997460793</v>
@@ -1762,7 +1762,7 @@
         <v>0.006674271603786346</v>
       </c>
       <c r="C80" s="2">
-        <v>121.4357080763981</v>
+        <v>121.435708076398</v>
       </c>
       <c r="D80" s="2">
         <v>0.006674271603786345</v>
@@ -1787,13 +1787,13 @@
         <v>84</v>
       </c>
       <c r="B82" s="2">
-        <v>0.003063062324578662</v>
+        <v>0.003063062324578663</v>
       </c>
       <c r="C82" s="2">
         <v>103.3156397339718</v>
       </c>
       <c r="D82" s="2">
-        <v>0.003063062324578661</v>
+        <v>0.003063062324578662</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1801,7 +1801,7 @@
         <v>85</v>
       </c>
       <c r="B83" s="2">
-        <v>0.01283849732236524</v>
+        <v>0.01283849732236523</v>
       </c>
       <c r="C83" s="2">
         <v>101.0725826868128</v>
@@ -1846,10 +1846,10 @@
         <v>0.01163183974330734</v>
       </c>
       <c r="C86" s="2">
-        <v>100.6622583955598</v>
+        <v>100.6622583955599</v>
       </c>
       <c r="D86" s="2">
-        <v>0.01163183974330733</v>
+        <v>0.01163183974330734</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1860,10 +1860,10 @@
         <v>0.005563922185213122</v>
       </c>
       <c r="C87" s="2">
-        <v>128.7324815389222</v>
+        <v>128.7324815389223</v>
       </c>
       <c r="D87" s="2">
-        <v>0.005563922185213122</v>
+        <v>0.005563922185213121</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1874,7 +1874,7 @@
         <v>0.02337999567124581</v>
       </c>
       <c r="C88" s="2">
-        <v>101.699913487983</v>
+        <v>101.6999134879831</v>
       </c>
       <c r="D88" s="2">
         <v>0.02337999567124581</v>
